--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_9_11.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_9_11.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15416.35924641446</v>
+        <v>8376.43830430601</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9829061.531704543</v>
+        <v>9853156.983341714</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22088418.71322985</v>
+        <v>22082679.38684229</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4211281.677884432</v>
+        <v>4212425.147014122</v>
       </c>
     </row>
     <row r="11">
@@ -8433,22 +8433,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>220.0898510449805</v>
+        <v>213.7089309661116</v>
       </c>
       <c r="L8" t="n">
-        <v>235.7664149699872</v>
+        <v>227.8503193726002</v>
       </c>
       <c r="M8" t="n">
-        <v>230.3462332272727</v>
+        <v>221.5380516068512</v>
       </c>
       <c r="N8" t="n">
-        <v>229.4130635965909</v>
+        <v>220.4623563888806</v>
       </c>
       <c r="O8" t="n">
-        <v>230.0982114216867</v>
+        <v>221.6463124176202</v>
       </c>
       <c r="P8" t="n">
-        <v>231.2329957552695</v>
+        <v>224.0194954968931</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8509,28 +8509,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J9" t="n">
-        <v>126.0910353404088</v>
+        <v>124.3018764260165</v>
       </c>
       <c r="K9" t="n">
-        <v>137.841438974359</v>
+        <v>133.5074379247318</v>
       </c>
       <c r="L9" t="n">
-        <v>138.5543797798742</v>
+        <v>132.7267805197011</v>
       </c>
       <c r="M9" t="n">
-        <v>142.1340339220183</v>
+        <v>135.3335004554958</v>
       </c>
       <c r="N9" t="n">
-        <v>131.3417120833333</v>
+        <v>124.3611887315708</v>
       </c>
       <c r="O9" t="n">
-        <v>142.5962444444444</v>
+        <v>136.210429333514</v>
       </c>
       <c r="P9" t="n">
-        <v>133.9744074143302</v>
+        <v>128.8492278044037</v>
       </c>
       <c r="Q9" t="n">
-        <v>139.9817740860215</v>
+        <v>136.5557272449332</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>134.8846762812383</v>
+        <v>131.5393333932398</v>
       </c>
       <c r="M10" t="n">
-        <v>138.9257839476051</v>
+        <v>135.3985889238948</v>
       </c>
       <c r="N10" t="n">
-        <v>127.6855444652332</v>
+        <v>124.2422182555182</v>
       </c>
       <c r="O10" t="n">
-        <v>138.4565384518428</v>
+        <v>135.2760693786741</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K11" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L11" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M11" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N11" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O11" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P11" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q11" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,13 +8746,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K12" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L12" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -8761,13 +8761,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3258104821802306</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q12" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L13" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M13" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N13" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O13" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P13" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K14" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L14" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M14" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N14" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O14" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P14" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q14" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,13 +8983,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K15" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L15" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3258104821803158</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q15" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L16" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M16" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N16" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O16" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P16" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K17" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L17" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M17" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N17" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O17" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P17" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q17" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,13 +9220,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K18" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L18" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -9235,13 +9235,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3258104821802874</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q18" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L19" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M19" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N19" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O19" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P19" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K20" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L20" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M20" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N20" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O20" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P20" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q20" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,13 +9457,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K21" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L21" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9472,13 +9472,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3258104821802874</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q21" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L22" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M22" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N22" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O22" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P22" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K23" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L23" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M23" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N23" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O23" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P23" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q23" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,13 +9694,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K24" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L24" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -9709,13 +9709,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3258104821802874</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q24" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L25" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M25" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N25" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O25" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P25" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K26" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L26" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M26" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N26" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O26" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P26" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q26" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,13 +9931,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K27" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L27" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -9946,13 +9946,13 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3258104821802874</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q27" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L28" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M28" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N28" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O28" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P28" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K29" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L29" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M29" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N29" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O29" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P29" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q29" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,13 +10168,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K30" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L30" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -10183,13 +10183,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0.3258104821802874</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q30" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L31" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M31" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N31" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O31" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P31" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K32" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L32" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M32" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N32" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O32" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P32" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q32" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,13 +10405,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K33" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L33" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -10420,13 +10420,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.3258104821802874</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q33" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L34" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M34" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N34" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O34" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P34" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K35" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L35" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M35" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N35" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O35" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P35" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q35" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,13 +10642,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K36" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L36" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -10657,13 +10657,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0.3258104821802306</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q36" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L37" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M37" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N37" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O37" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P37" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K38" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L38" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M38" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N38" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O38" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P38" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q38" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,13 +10879,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K39" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L39" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -10894,13 +10894,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0.3258104821802306</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q39" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L40" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M40" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N40" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O40" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P40" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K41" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L41" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M41" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N41" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O41" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P41" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q41" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,13 +11116,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K42" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L42" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -11131,13 +11131,13 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.3258104821802874</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q42" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L43" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M43" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N43" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O43" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P43" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>86.19202512970135</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K44" t="n">
-        <v>77.92847416055844</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L44" t="n">
-        <v>59.40265617601736</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M44" t="n">
-        <v>34.10756991068982</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N44" t="n">
-        <v>29.99905354633964</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O44" t="n">
-        <v>41.79721644681234</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P44" t="n">
-        <v>70.52245304170171</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q44" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,13 +11353,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>70.3433059119497</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K45" t="n">
-        <v>41.28364652152879</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L45" t="n">
-        <v>8.720511855345876</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -11368,13 +11368,13 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0.3258104821802874</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>19.78984137659438</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q45" t="n">
-        <v>63.65241559545547</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>70.76997948201081</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L46" t="n">
-        <v>60.35333201894319</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M46" t="n">
-        <v>60.34293148858868</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N46" t="n">
-        <v>50.97121659638069</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O46" t="n">
-        <v>67.59844009118703</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P46" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -22993,16 +22993,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>415.302737515135</v>
+        <v>415.2525745279679</v>
       </c>
       <c r="H8" t="n">
-        <v>339.4748021157671</v>
+        <v>338.9610704234411</v>
       </c>
       <c r="I8" t="n">
-        <v>210.4758895704059</v>
+        <v>208.5419810076426</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>7.691768522530872</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,19 +23023,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>4.573660934093467</v>
       </c>
       <c r="R8" t="n">
-        <v>149.8691179411497</v>
+        <v>146.7180671985084</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862453</v>
+        <v>207.8769805161729</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0958495641314</v>
+        <v>222.876261087807</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3456529078365</v>
+        <v>251.3416398688631</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23072,16 +23072,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3435171632106</v>
+        <v>137.3166775988975</v>
       </c>
       <c r="H9" t="n">
-        <v>112.2354442364965</v>
+        <v>111.9762305495779</v>
       </c>
       <c r="I9" t="n">
-        <v>89.39663285141508</v>
+        <v>88.47255136081093</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23105,16 +23105,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>100.1578341526431</v>
+        <v>98.49142681748486</v>
       </c>
       <c r="S9" t="n">
-        <v>171.6831711038378</v>
+        <v>171.1846379684609</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1647286948216</v>
+        <v>200.0565464158579</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9413820809748</v>
+        <v>225.9396163201648</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9909793584588</v>
+        <v>167.9684779693381</v>
       </c>
       <c r="H10" t="n">
-        <v>162.2271725074396</v>
+        <v>162.0271147023483</v>
       </c>
       <c r="I10" t="n">
-        <v>155.4504749272583</v>
+        <v>154.7737967889741</v>
       </c>
       <c r="J10" t="n">
-        <v>93.35918011667277</v>
+        <v>91.76833190583969</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>19.65523952622401</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,22 +23178,22 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>86.16204325169439</v>
+        <v>84.27785874996061</v>
       </c>
       <c r="R10" t="n">
-        <v>177.2933913771695</v>
+        <v>176.2816470990699</v>
       </c>
       <c r="S10" t="n">
-        <v>224.0165980369723</v>
+        <v>223.6244601920234</v>
       </c>
       <c r="T10" t="n">
-        <v>227.9455894282815</v>
+        <v>227.8494471293112</v>
       </c>
       <c r="U10" t="n">
-        <v>286.3190293564909</v>
+        <v>286.3178020079934</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H11" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I11" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S11" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T11" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H12" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I12" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S12" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T12" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H13" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I13" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J13" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R13" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S13" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T13" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H14" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I14" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S14" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T14" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H15" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I15" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S15" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T15" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H16" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I16" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J16" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R16" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S16" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T16" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H17" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I17" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S17" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T17" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H18" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I18" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S18" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T18" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H19" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I19" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J19" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R19" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S19" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T19" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H20" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I20" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S20" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T20" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H21" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I21" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S21" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T21" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H22" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I22" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J22" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R22" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S22" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T22" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H23" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I23" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S23" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T23" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H24" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I24" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S24" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T24" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H25" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I25" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J25" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R25" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S25" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T25" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H26" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I26" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S26" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T26" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H27" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I27" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S27" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T27" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H28" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I28" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J28" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R28" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S28" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T28" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H29" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I29" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S29" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T29" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H30" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I30" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S30" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T30" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H31" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I31" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J31" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R31" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S31" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T31" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H32" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I32" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S32" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T32" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H33" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I33" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S33" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T33" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H34" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I34" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J34" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R34" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S34" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T34" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H35" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I35" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S35" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T35" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H36" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I36" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S36" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T36" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H37" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I37" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J37" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R37" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S37" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T37" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H38" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I38" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S38" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T38" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H39" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I39" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S39" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T39" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H40" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I40" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J40" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R40" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S40" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T40" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H41" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I41" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S41" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T41" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H42" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I42" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S42" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T42" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H43" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I43" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J43" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R43" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S43" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T43" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H44" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I44" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>79.66643452406424</v>
+        <v>79.50566485817191</v>
       </c>
       <c r="S44" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T44" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H45" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I45" t="n">
-        <v>68.80889700235846</v>
+        <v>68.761749468207</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>63.03172094509595</v>
+        <v>62.94669922618533</v>
       </c>
       <c r="S45" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T45" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H46" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I46" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J46" t="n">
-        <v>57.91645880519737</v>
+        <v>57.83529218611377</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>44.18404325169438</v>
+        <v>44.08791033046781</v>
       </c>
       <c r="R46" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S46" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T46" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>365525.1788069177</v>
+        <v>366830.7364104902</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>363758.3413574412</v>
+        <v>363751.0125505875</v>
       </c>
     </row>
   </sheetData>
@@ -26267,43 +26267,43 @@
         <v>59129.07304229552</v>
       </c>
       <c r="D2" t="n">
-        <v>59129.07304229551</v>
+        <v>59617.75405590846</v>
       </c>
       <c r="E2" t="n">
-        <v>64973.66859233286</v>
+        <v>64985.55566641795</v>
       </c>
       <c r="F2" t="n">
-        <v>64973.66859233286</v>
+        <v>64985.55566641795</v>
       </c>
       <c r="G2" t="n">
-        <v>64973.66859233286</v>
+        <v>64985.55566641795</v>
       </c>
       <c r="H2" t="n">
-        <v>64973.66859233286</v>
+        <v>64985.55566641795</v>
       </c>
       <c r="I2" t="n">
-        <v>64973.66859233287</v>
+        <v>64985.55566641795</v>
       </c>
       <c r="J2" t="n">
-        <v>64973.66859233287</v>
+        <v>64985.55566641795</v>
       </c>
       <c r="K2" t="n">
-        <v>64973.66859233287</v>
+        <v>64985.55566641795</v>
       </c>
       <c r="L2" t="n">
-        <v>64973.66859233287</v>
+        <v>64985.55566641795</v>
       </c>
       <c r="M2" t="n">
-        <v>64973.66859233286</v>
+        <v>64985.55566641795</v>
       </c>
       <c r="N2" t="n">
-        <v>64973.66859233287</v>
+        <v>64985.55566641795</v>
       </c>
       <c r="O2" t="n">
-        <v>64973.66859233287</v>
+        <v>64985.55566641795</v>
       </c>
       <c r="P2" t="n">
-        <v>64973.66859233287</v>
+        <v>64985.55566641795</v>
       </c>
     </row>
     <row r="3">
@@ -26319,10 +26319,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>10686.3707673366</v>
       </c>
       <c r="E3" t="n">
-        <v>223346.034</v>
+        <v>213832.6167554025</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48378.33248915087</v>
+        <v>49942.83355433132</v>
       </c>
       <c r="C4" t="n">
-        <v>48378.33248915088</v>
+        <v>49942.83355433132</v>
       </c>
       <c r="D4" t="n">
-        <v>48378.33248915087</v>
+        <v>48584.74050141103</v>
       </c>
       <c r="E4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
       <c r="F4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
       <c r="G4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
       <c r="H4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
       <c r="I4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
       <c r="J4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
       <c r="K4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
       <c r="L4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
       <c r="M4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
       <c r="N4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
       <c r="O4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
       <c r="P4" t="n">
-        <v>15263.20981674642</v>
+        <v>15683.41930441445</v>
       </c>
     </row>
     <row r="5">
@@ -26423,43 +26423,43 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>33627.6</v>
+        <v>33899.6213386609</v>
       </c>
       <c r="E5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="F5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="G5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="H5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="I5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="J5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="K5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="L5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="M5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="N5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="O5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
       <c r="P5" t="n">
-        <v>6060.400000000001</v>
+        <v>6074.278792600922</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-22876.85944685536</v>
+        <v>-24441.36051203579</v>
       </c>
       <c r="C6" t="n">
-        <v>-22876.85944685536</v>
+        <v>-24441.36051203579</v>
       </c>
       <c r="D6" t="n">
-        <v>-22876.85944685536</v>
+        <v>-33552.97855150008</v>
       </c>
       <c r="E6" t="n">
-        <v>-179695.9752244136</v>
+        <v>-170604.7591859999</v>
       </c>
       <c r="F6" t="n">
-        <v>43650.05877558643</v>
+        <v>43227.85756940258</v>
       </c>
       <c r="G6" t="n">
-        <v>43650.05877558643</v>
+        <v>43227.85756940258</v>
       </c>
       <c r="H6" t="n">
-        <v>43650.05877558643</v>
+        <v>43227.85756940258</v>
       </c>
       <c r="I6" t="n">
-        <v>43650.05877558645</v>
+        <v>43227.85756940258</v>
       </c>
       <c r="J6" t="n">
-        <v>43650.05877558645</v>
+        <v>43227.85756940258</v>
       </c>
       <c r="K6" t="n">
-        <v>43650.05877558645</v>
+        <v>43227.85756940258</v>
       </c>
       <c r="L6" t="n">
-        <v>43650.05877558645</v>
+        <v>43227.85756940258</v>
       </c>
       <c r="M6" t="n">
-        <v>43650.05877558645</v>
+        <v>43227.85756940258</v>
       </c>
       <c r="N6" t="n">
-        <v>43650.05877558645</v>
+        <v>43227.85756940258</v>
       </c>
       <c r="O6" t="n">
-        <v>43650.05877558645</v>
+        <v>43227.85756940258</v>
       </c>
       <c r="P6" t="n">
-        <v>43650.05877558645</v>
+        <v>43227.85756940258</v>
       </c>
     </row>
   </sheetData>
@@ -26681,43 +26681,43 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>12.47804305783955</v>
       </c>
       <c r="E3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="F3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="G3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="H3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="I3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="J3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="K3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="L3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="M3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="N3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="O3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="P3" t="n">
-        <v>278</v>
+        <v>278.6366418624276</v>
       </c>
     </row>
     <row r="4">
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26898,43 +26898,43 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>12.47804305783955</v>
       </c>
       <c r="E3" t="n">
-        <v>278</v>
+        <v>266.1585988045881</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.05016298716719412</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.5137316923260269</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.933908562763253</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>4.257520832081646</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6.380920078868974</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>7.916095597386993</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>8.80818162042158</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>8.950707207710371</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>8.451899004066584</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>7.213500258376478</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.417038280451338</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.15105074264126</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.143089070072437</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.2195884763243924</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.004013038973375529</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.02683956431308884</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.2592136869185159</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.9240814906041552</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.535750240650205</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4.334001049627156</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>5.827599260173083</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6.800533466522552</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6.980523351762521</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>6.385815110930395</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>5.125179609926587</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.426046841088322</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.666407335158271</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.498533135376891</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1081822789637221</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.001765760810071635</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.02250138912069426</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.2000578050912637</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.6766781382841512</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.590848210833084</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2.614252299658842</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.345342887998491</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.527195023710282</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.443326209714971</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.180469073168677</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.884184501733771</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.01174427809958</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.3921378449488262</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.09614229897023908</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.001227348497492416</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H11" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I11" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J11" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K11" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L11" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M11" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N11" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O11" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P11" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R11" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S11" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T11" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,22 +31749,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H12" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I12" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J12" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K12" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L12" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M12" t="n">
         <v>142.1340339220183</v>
@@ -31773,25 +31773,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>142.2704339622642</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q12" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R12" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S12" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T12" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H13" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I13" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J13" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K13" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L13" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M13" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N13" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O13" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P13" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R13" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S13" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T13" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H14" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I14" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J14" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K14" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L14" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M14" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N14" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O14" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P14" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q14" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R14" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S14" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T14" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,22 +31986,22 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H15" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I15" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J15" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K15" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L15" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M15" t="n">
         <v>142.1340339220183</v>
@@ -32010,25 +32010,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>142.2704339622641</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q15" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R15" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S15" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T15" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H16" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I16" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J16" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K16" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L16" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M16" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N16" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O16" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P16" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R16" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S16" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T16" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H17" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I17" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J17" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K17" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L17" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M17" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N17" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O17" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P17" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q17" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R17" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S17" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T17" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,22 +32223,22 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H18" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I18" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J18" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K18" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L18" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
@@ -32247,25 +32247,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>142.2704339622641</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q18" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R18" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S18" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T18" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U18" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H19" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I19" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J19" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K19" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L19" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M19" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N19" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O19" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P19" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R19" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S19" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T19" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H20" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I20" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J20" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K20" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L20" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M20" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N20" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O20" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P20" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q20" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R20" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S20" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T20" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,22 +32460,22 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H21" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I21" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J21" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K21" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L21" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M21" t="n">
         <v>142.1340339220183</v>
@@ -32484,25 +32484,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>142.2704339622641</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q21" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R21" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S21" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T21" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U21" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H22" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I22" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J22" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K22" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L22" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M22" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N22" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O22" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P22" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q22" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R22" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S22" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T22" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H23" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I23" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J23" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K23" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L23" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M23" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N23" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O23" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P23" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q23" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R23" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S23" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T23" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,22 +32697,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H24" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I24" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J24" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K24" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L24" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M24" t="n">
         <v>142.1340339220183</v>
@@ -32721,25 +32721,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>142.2704339622641</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q24" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R24" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S24" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T24" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H25" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I25" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J25" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K25" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L25" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M25" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N25" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O25" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P25" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q25" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R25" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S25" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T25" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H26" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I26" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J26" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K26" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L26" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M26" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N26" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O26" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P26" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q26" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R26" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S26" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T26" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U26" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,22 +32934,22 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H27" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I27" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J27" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K27" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L27" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
@@ -32958,25 +32958,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>142.2704339622641</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q27" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R27" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S27" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T27" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U27" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H28" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I28" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J28" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K28" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L28" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M28" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N28" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O28" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P28" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q28" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R28" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S28" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T28" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U28" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H29" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I29" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J29" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K29" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L29" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M29" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N29" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O29" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P29" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q29" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R29" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S29" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T29" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U29" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,22 +33171,22 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H30" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I30" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J30" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K30" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L30" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M30" t="n">
         <v>142.1340339220183</v>
@@ -33195,25 +33195,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>142.2704339622641</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q30" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R30" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S30" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T30" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U30" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H31" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I31" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J31" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K31" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L31" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M31" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N31" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O31" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P31" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q31" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R31" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S31" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T31" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U31" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H32" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I32" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J32" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K32" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L32" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M32" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N32" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O32" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P32" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q32" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R32" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S32" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T32" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U32" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,22 +33408,22 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H33" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I33" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J33" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K33" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L33" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M33" t="n">
         <v>142.1340339220183</v>
@@ -33432,25 +33432,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>142.2704339622641</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q33" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R33" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S33" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T33" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U33" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H34" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I34" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J34" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K34" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L34" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M34" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N34" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O34" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P34" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q34" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R34" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S34" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T34" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U34" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H35" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I35" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J35" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K35" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L35" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M35" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N35" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O35" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P35" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q35" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R35" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S35" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T35" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U35" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,22 +33645,22 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H36" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I36" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J36" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K36" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L36" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M36" t="n">
         <v>142.1340339220183</v>
@@ -33669,25 +33669,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>142.2704339622642</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q36" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R36" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S36" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T36" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U36" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H37" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I37" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J37" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K37" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L37" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M37" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N37" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O37" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P37" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q37" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R37" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S37" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T37" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U37" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H38" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I38" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J38" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K38" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L38" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M38" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N38" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O38" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P38" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q38" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R38" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S38" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T38" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,22 +33882,22 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H39" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I39" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J39" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K39" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L39" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M39" t="n">
         <v>142.1340339220183</v>
@@ -33906,25 +33906,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>142.2704339622642</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q39" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R39" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S39" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T39" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H40" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I40" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J40" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K40" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L40" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M40" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N40" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O40" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P40" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q40" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R40" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S40" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T40" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U40" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H41" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I41" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J41" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K41" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L41" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M41" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N41" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O41" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P41" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q41" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R41" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S41" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T41" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U41" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,22 +34119,22 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H42" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I42" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J42" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K42" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L42" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
@@ -34143,25 +34143,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>142.2704339622641</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q42" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R42" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S42" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T42" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U42" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H43" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I43" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J43" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K43" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L43" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M43" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N43" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O43" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P43" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q43" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R43" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S43" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T43" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.117587939698492</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H44" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I44" t="n">
-        <v>43.08580904522614</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J44" t="n">
-        <v>94.85387939698494</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K44" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L44" t="n">
-        <v>176.3637587939699</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M44" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N44" t="n">
-        <v>199.4140100502513</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O44" t="n">
-        <v>188.3009949748744</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P44" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q44" t="n">
-        <v>120.6869246231156</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R44" t="n">
-        <v>70.20268341708544</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S44" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T44" t="n">
-        <v>4.89224120603015</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08940703517587931</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,22 +34356,22 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5979622641509434</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H45" t="n">
-        <v>5.775056603773586</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I45" t="n">
-        <v>20.58773584905661</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J45" t="n">
-        <v>56.49432075471699</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K45" t="n">
-        <v>96.5577924528302</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L45" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M45" t="n">
         <v>142.1340339220183</v>
@@ -34380,25 +34380,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O45" t="n">
-        <v>142.2704339622641</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>114.1845660377359</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q45" t="n">
-        <v>76.32935849056605</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R45" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S45" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T45" t="n">
-        <v>2.410207547169811</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U45" t="n">
-        <v>0.03933962264150945</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.501311475409836</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H46" t="n">
-        <v>4.457114754098363</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I46" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J46" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K46" t="n">
-        <v>58.24327868852457</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L46" t="n">
-        <v>74.53134426229509</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M46" t="n">
-        <v>78.58285245901638</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N46" t="n">
-        <v>76.71432786885251</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O46" t="n">
-        <v>70.85809836065576</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P46" t="n">
-        <v>60.63134426229505</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q46" t="n">
-        <v>41.978</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R46" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S46" t="n">
-        <v>8.736491803278685</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T46" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U46" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
